--- a/output/graficos_nacionales/plot_nacional_regiones_d_apoyopot_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_d_apoyopot_a_2021.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 21:39</t>
+    <t xml:space="preserve">2026-08-21 12:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_d_apoyopot_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_d_apoyopot_a_2021.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Regiones'!$A$1:$B$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Regiones'!$A$1:$B$17</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -66,6 +66,9 @@
     <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
@@ -75,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-21 12:48</t>
+    <t xml:space="preserve">2026-09-04 19:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -511,7 +514,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.78</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="6">
@@ -599,11 +602,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="n">
         <v>2.79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B16"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -620,7 +631,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -628,50 +639,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_regiones_d_apoyopot_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_d_apoyopot_a_2021.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 19:56</t>
+    <t xml:space="preserve">2026-09-07 12:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
